--- a/excel/day5-6.xlsx
+++ b/excel/day5-6.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6181C92-077C-40C8-9B2C-F500ADFFA574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D963A9B-A790-44CD-99D1-F7F34B6C7D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sales" sheetId="1" r:id="rId1"/>
     <sheet name="Report" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sales!$A$1:$N$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sales!$A$1:$P$31</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="96">
   <si>
     <t>Date</t>
   </si>
@@ -92,6 +92,12 @@
     <t>E/H/M/L</t>
   </si>
   <si>
+    <t>East and Completed</t>
+  </si>
+  <si>
+    <t>Electronics or Office</t>
+  </si>
+  <si>
     <t>Channel</t>
   </si>
   <si>
@@ -315,6 +321,30 @@
   </si>
   <si>
     <t>8. Classify each order as Excellent, High, Medium, Low</t>
+  </si>
+  <si>
+    <t>9. Orders from east and completed</t>
+  </si>
+  <si>
+    <t>10. Orders from electronics or office</t>
+  </si>
+  <si>
+    <t>11. How many completed orders</t>
+  </si>
+  <si>
+    <t>12. How many completed orders in east</t>
+  </si>
+  <si>
+    <t>13. Total sales for east</t>
+  </si>
+  <si>
+    <t>14. Total completed sales for east</t>
+  </si>
+  <si>
+    <t>15. Average sales for electronics orders</t>
+  </si>
+  <si>
+    <t>16. Average completed sales for east</t>
   </si>
 </sst>
 </file>
@@ -322,7 +352,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -397,7 +427,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -706,7 +736,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
@@ -715,12 +745,12 @@
     <col min="7" max="7" width="10" customWidth="1"/>
     <col min="8" max="9" width="12" customWidth="1"/>
     <col min="10" max="10" width="16.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.5703125" style="5" customWidth="1"/>
-    <col min="12" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="11" max="13" width="16.5703125" style="5" customWidth="1"/>
+    <col min="14" max="15" width="12" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -754,34 +784,40 @@
       <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" s="2">
         <v>46027</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -800,34 +836,42 @@
         <f t="array" ref="K2">_xlfn.IFS(I2&lt;750, "Low", AND(I2&gt;=750, I2&lt;=1499), "Medium", AND(I2&gt;=1500, I2&lt;=2499), "High", I2&gt;=2500, "Excellent")</f>
         <v>High</v>
       </c>
-      <c r="L2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" t="s">
-        <v>20</v>
+      <c r="L2" s="6" t="b">
+        <f>AND(B2="East", O2="Completed")</f>
+        <v>1</v>
+      </c>
+      <c r="M2" s="6" t="b">
+        <f>OR(E2="Electronics", E2="Office")</f>
+        <v>1</v>
       </c>
       <c r="N2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" t="s">
+        <v>22</v>
+      </c>
+      <c r="P2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" s="2">
         <v>46029</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -846,34 +890,42 @@
         <f t="array" ref="K3">_xlfn.IFS(I3&lt;750, "Low", AND(I3&gt;=750, I3&lt;=1499), "Medium", AND(I3&gt;=1500, I3&lt;=2499), "High", I3&gt;=2500, "Excellent")</f>
         <v>Medium</v>
       </c>
-      <c r="L3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" t="s">
-        <v>20</v>
+      <c r="L3" s="6" t="b">
+        <f t="shared" ref="L3:L31" si="1">AND(B3="East", O3="Completed")</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="6" t="b">
+        <f t="shared" ref="M3:M31" si="2">OR(E3="Electronics", E3="Office")</f>
+        <v>1</v>
       </c>
       <c r="N3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>29</v>
+      </c>
+      <c r="O3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" s="2">
         <v>46034</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -892,34 +944,42 @@
         <f t="array" ref="K4">_xlfn.IFS(I4&lt;750, "Low", AND(I4&gt;=750, I4&lt;=1499), "Medium", AND(I4&gt;=1500, I4&lt;=2499), "High", I4&gt;=2500, "Excellent")</f>
         <v>Medium</v>
       </c>
-      <c r="L4" t="s">
-        <v>19</v>
-      </c>
-      <c r="M4" t="s">
-        <v>20</v>
+      <c r="L4" s="6" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M4" s="6" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>21</v>
+      </c>
+      <c r="O4" t="s">
+        <v>22</v>
+      </c>
+      <c r="P4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" s="2">
         <v>46040</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -938,34 +998,42 @@
         <f t="array" ref="K5">_xlfn.IFS(I5&lt;750, "Low", AND(I5&gt;=750, I5&lt;=1499), "Medium", AND(I5&gt;=1500, I5&lt;=2499), "High", I5&gt;=2500, "Excellent")</f>
         <v>Medium</v>
       </c>
-      <c r="L5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M5" t="s">
-        <v>37</v>
+      <c r="L5" s="6" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M5" s="6" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>29</v>
+      </c>
+      <c r="O5" t="s">
+        <v>39</v>
+      </c>
+      <c r="P5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" s="2">
         <v>46046</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6">
         <v>10</v>
@@ -984,34 +1052,42 @@
         <f t="array" ref="K6">_xlfn.IFS(I6&lt;750, "Low", AND(I6&gt;=750, I6&lt;=1499), "Medium", AND(I6&gt;=1500, I6&lt;=2499), "High", I6&gt;=2500, "Excellent")</f>
         <v>Low</v>
       </c>
-      <c r="L6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M6" t="s">
-        <v>20</v>
+      <c r="L6" s="6" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M6" s="6" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="N6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>21</v>
+      </c>
+      <c r="O6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" s="2">
         <v>46056</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G7">
         <v>6</v>
@@ -1030,34 +1106,42 @@
         <f t="array" ref="K7">_xlfn.IFS(I7&lt;750, "Low", AND(I7&gt;=750, I7&lt;=1499), "Medium", AND(I7&gt;=1500, I7&lt;=2499), "High", I7&gt;=2500, "Excellent")</f>
         <v>Excellent</v>
       </c>
-      <c r="L7" t="s">
-        <v>19</v>
-      </c>
-      <c r="M7" t="s">
-        <v>20</v>
+      <c r="L7" s="6" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M7" s="6" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7" t="s">
+        <v>22</v>
+      </c>
+      <c r="P7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" s="2">
         <v>46061</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G8">
         <v>8</v>
@@ -1076,34 +1160,42 @@
         <f t="array" ref="K8">_xlfn.IFS(I8&lt;750, "Low", AND(I8&gt;=750, I8&lt;=1499), "Medium", AND(I8&gt;=1500, I8&lt;=2499), "High", I8&gt;=2500, "Excellent")</f>
         <v>Medium</v>
       </c>
-      <c r="L8" t="s">
-        <v>27</v>
-      </c>
-      <c r="M8" t="s">
-        <v>20</v>
+      <c r="L8" s="6" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M8" s="6" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="N8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>29</v>
+      </c>
+      <c r="O8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" s="2">
         <v>46067</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1122,34 +1214,42 @@
         <f t="array" ref="K9">_xlfn.IFS(I9&lt;750, "Low", AND(I9&gt;=750, I9&lt;=1499), "Medium", AND(I9&gt;=1500, I9&lt;=2499), "High", I9&gt;=2500, "Excellent")</f>
         <v>Medium</v>
       </c>
-      <c r="L9" t="s">
-        <v>27</v>
-      </c>
-      <c r="M9" t="s">
-        <v>50</v>
+      <c r="L9" s="6" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M9" s="6" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>29</v>
+      </c>
+      <c r="O9" t="s">
+        <v>52</v>
+      </c>
+      <c r="P9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" s="2">
         <v>46074</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G10">
         <v>3</v>
@@ -1168,34 +1268,42 @@
         <f t="array" ref="K10">_xlfn.IFS(I10&lt;750, "Low", AND(I10&gt;=750, I10&lt;=1499), "Medium", AND(I10&gt;=1500, I10&lt;=2499), "High", I10&gt;=2500, "Excellent")</f>
         <v>Excellent</v>
       </c>
-      <c r="L10" t="s">
-        <v>19</v>
-      </c>
-      <c r="M10" t="s">
-        <v>20</v>
+      <c r="L10" s="6" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M10" s="6" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N10" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10" t="s">
+        <v>22</v>
+      </c>
+      <c r="P10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" s="2">
         <v>46080</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G11">
         <v>15</v>
@@ -1214,34 +1322,42 @@
         <f t="array" ref="K11">_xlfn.IFS(I11&lt;750, "Low", AND(I11&gt;=750, I11&lt;=1499), "Medium", AND(I11&gt;=1500, I11&lt;=2499), "High", I11&gt;=2500, "Excellent")</f>
         <v>Low</v>
       </c>
-      <c r="L11" t="s">
-        <v>19</v>
-      </c>
-      <c r="M11" t="s">
-        <v>20</v>
+      <c r="L11" s="6" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M11" s="6" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="N11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>21</v>
+      </c>
+      <c r="O11" t="s">
+        <v>22</v>
+      </c>
+      <c r="P11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" s="2">
         <v>46085</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G12">
         <v>4</v>
@@ -1260,34 +1376,42 @@
         <f t="array" ref="K12">_xlfn.IFS(I12&lt;750, "Low", AND(I12&gt;=750, I12&lt;=1499), "Medium", AND(I12&gt;=1500, I12&lt;=2499), "High", I12&gt;=2500, "Excellent")</f>
         <v>Medium</v>
       </c>
-      <c r="L12" t="s">
-        <v>27</v>
-      </c>
-      <c r="M12" t="s">
-        <v>20</v>
+      <c r="L12" s="6" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M12" s="6" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>29</v>
+      </c>
+      <c r="O12" t="s">
+        <v>22</v>
+      </c>
+      <c r="P12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" s="2">
         <v>46091</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -1306,34 +1430,42 @@
         <f t="array" ref="K13">_xlfn.IFS(I13&lt;750, "Low", AND(I13&gt;=750, I13&lt;=1499), "Medium", AND(I13&gt;=1500, I13&lt;=2499), "High", I13&gt;=2500, "Excellent")</f>
         <v>High</v>
       </c>
-      <c r="L13" t="s">
-        <v>19</v>
-      </c>
-      <c r="M13" t="s">
-        <v>37</v>
+      <c r="L13" s="6" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M13" s="6" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N13" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O13" t="s">
+        <v>39</v>
+      </c>
+      <c r="P13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" s="2">
         <v>46097</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G14">
         <v>12</v>
@@ -1352,34 +1484,42 @@
         <f t="array" ref="K14">_xlfn.IFS(I14&lt;750, "Low", AND(I14&gt;=750, I14&lt;=1499), "Medium", AND(I14&gt;=1500, I14&lt;=2499), "High", I14&gt;=2500, "Excellent")</f>
         <v>Medium</v>
       </c>
-      <c r="L14" t="s">
-        <v>27</v>
-      </c>
-      <c r="M14" t="s">
-        <v>20</v>
+      <c r="L14" s="6" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M14" s="6" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="N14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+        <v>29</v>
+      </c>
+      <c r="O14" t="s">
+        <v>22</v>
+      </c>
+      <c r="P14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" s="2">
         <v>46103</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F15" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G15">
         <v>7</v>
@@ -1398,34 +1538,42 @@
         <f t="array" ref="K15">_xlfn.IFS(I15&lt;750, "Low", AND(I15&gt;=750, I15&lt;=1499), "Medium", AND(I15&gt;=1500, I15&lt;=2499), "High", I15&gt;=2500, "Excellent")</f>
         <v>Medium</v>
       </c>
-      <c r="L15" t="s">
-        <v>19</v>
-      </c>
-      <c r="M15" t="s">
-        <v>20</v>
+      <c r="L15" s="6" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M15" s="6" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+        <v>21</v>
+      </c>
+      <c r="O15" t="s">
+        <v>22</v>
+      </c>
+      <c r="P15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" s="2">
         <v>46109</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D16" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G16">
         <v>3</v>
@@ -1444,34 +1592,42 @@
         <f t="array" ref="K16">_xlfn.IFS(I16&lt;750, "Low", AND(I16&gt;=750, I16&lt;=1499), "Medium", AND(I16&gt;=1500, I16&lt;=2499), "High", I16&gt;=2500, "Excellent")</f>
         <v>Medium</v>
       </c>
-      <c r="L16" t="s">
-        <v>27</v>
-      </c>
-      <c r="M16" t="s">
-        <v>20</v>
+      <c r="L16" s="6" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="6" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N16" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+        <v>29</v>
+      </c>
+      <c r="O16" t="s">
+        <v>22</v>
+      </c>
+      <c r="P16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="2">
         <v>46115</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E17" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G17">
         <v>10</v>
@@ -1490,34 +1646,42 @@
         <f t="array" ref="K17">_xlfn.IFS(I17&lt;750, "Low", AND(I17&gt;=750, I17&lt;=1499), "Medium", AND(I17&gt;=1500, I17&lt;=2499), "High", I17&gt;=2500, "Excellent")</f>
         <v>Medium</v>
       </c>
-      <c r="L17" t="s">
-        <v>19</v>
-      </c>
-      <c r="M17" t="s">
-        <v>20</v>
+      <c r="L17" s="6" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M17" s="6" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="N17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+        <v>21</v>
+      </c>
+      <c r="O17" t="s">
+        <v>22</v>
+      </c>
+      <c r="P17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" s="2">
         <v>46121</v>
       </c>
       <c r="B18" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" t="s">
         <v>51</v>
-      </c>
-      <c r="D18" t="s">
-        <v>63</v>
-      </c>
-      <c r="E18" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" t="s">
-        <v>49</v>
       </c>
       <c r="G18">
         <v>4</v>
@@ -1536,34 +1700,42 @@
         <f t="array" ref="K18">_xlfn.IFS(I18&lt;750, "Low", AND(I18&gt;=750, I18&lt;=1499), "Medium", AND(I18&gt;=1500, I18&lt;=2499), "High", I18&gt;=2500, "Excellent")</f>
         <v>High</v>
       </c>
-      <c r="L18" t="s">
-        <v>27</v>
-      </c>
-      <c r="M18" t="s">
-        <v>20</v>
+      <c r="L18" s="6" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M18" s="6" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N18" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+        <v>29</v>
+      </c>
+      <c r="O18" t="s">
+        <v>22</v>
+      </c>
+      <c r="P18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" s="2">
         <v>46127</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D19" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1582,34 +1754,42 @@
         <f t="array" ref="K19">_xlfn.IFS(I19&lt;750, "Low", AND(I19&gt;=750, I19&lt;=1499), "Medium", AND(I19&gt;=1500, I19&lt;=2499), "High", I19&gt;=2500, "Excellent")</f>
         <v>Medium</v>
       </c>
-      <c r="L19" t="s">
-        <v>19</v>
-      </c>
-      <c r="M19" t="s">
-        <v>37</v>
+      <c r="L19" s="6" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="6" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N19" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+        <v>21</v>
+      </c>
+      <c r="O19" t="s">
+        <v>39</v>
+      </c>
+      <c r="P19" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" s="2">
         <v>46133</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D20" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E20" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F20" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G20">
         <v>20</v>
@@ -1628,34 +1808,42 @@
         <f t="array" ref="K20">_xlfn.IFS(I20&lt;750, "Low", AND(I20&gt;=750, I20&lt;=1499), "Medium", AND(I20&gt;=1500, I20&lt;=2499), "High", I20&gt;=2500, "Excellent")</f>
         <v>Medium</v>
       </c>
-      <c r="L20" t="s">
-        <v>27</v>
-      </c>
-      <c r="M20" t="s">
-        <v>20</v>
+      <c r="L20" s="6" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M20" s="6" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="N20" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+        <v>29</v>
+      </c>
+      <c r="O20" t="s">
+        <v>22</v>
+      </c>
+      <c r="P20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" s="2">
         <v>46139</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D21" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E21" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F21" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -1674,34 +1862,42 @@
         <f t="array" ref="K21">_xlfn.IFS(I21&lt;750, "Low", AND(I21&gt;=750, I21&lt;=1499), "Medium", AND(I21&gt;=1500, I21&lt;=2499), "High", I21&gt;=2500, "Excellent")</f>
         <v>Low</v>
       </c>
-      <c r="L21" t="s">
-        <v>19</v>
-      </c>
-      <c r="M21" t="s">
-        <v>50</v>
+      <c r="L21" s="6" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M21" s="6" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N21" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+        <v>21</v>
+      </c>
+      <c r="O21" t="s">
+        <v>52</v>
+      </c>
+      <c r="P21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" s="2">
         <v>46144</v>
       </c>
       <c r="B22" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E22" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G22">
         <v>8</v>
@@ -1720,34 +1916,42 @@
         <f t="array" ref="K22">_xlfn.IFS(I22&lt;750, "Low", AND(I22&gt;=750, I22&lt;=1499), "Medium", AND(I22&gt;=1500, I22&lt;=2499), "High", I22&gt;=2500, "Excellent")</f>
         <v>Excellent</v>
       </c>
-      <c r="L22" t="s">
-        <v>19</v>
-      </c>
-      <c r="M22" t="s">
-        <v>20</v>
+      <c r="L22" s="6" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M22" s="6" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N22" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="O22" t="s">
+        <v>22</v>
+      </c>
+      <c r="P22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
       <c r="A23" s="2">
         <v>46150</v>
       </c>
       <c r="B23" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D23" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E23" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F23" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G23">
         <v>18</v>
@@ -1766,34 +1970,42 @@
         <f t="array" ref="K23">_xlfn.IFS(I23&lt;750, "Low", AND(I23&gt;=750, I23&lt;=1499), "Medium", AND(I23&gt;=1500, I23&lt;=2499), "High", I23&gt;=2500, "Excellent")</f>
         <v>Medium</v>
       </c>
-      <c r="L23" t="s">
-        <v>27</v>
-      </c>
-      <c r="M23" t="s">
-        <v>20</v>
+      <c r="L23" s="6" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M23" s="6" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="N23" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+        <v>29</v>
+      </c>
+      <c r="O23" t="s">
+        <v>22</v>
+      </c>
+      <c r="P23" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24" s="2">
         <v>46156</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C24" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D24" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E24" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F24" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G24">
         <v>6</v>
@@ -1812,34 +2024,42 @@
         <f t="array" ref="K24">_xlfn.IFS(I24&lt;750, "Low", AND(I24&gt;=750, I24&lt;=1499), "Medium", AND(I24&gt;=1500, I24&lt;=2499), "High", I24&gt;=2500, "Excellent")</f>
         <v>Medium</v>
       </c>
-      <c r="L24" t="s">
-        <v>19</v>
-      </c>
-      <c r="M24" t="s">
-        <v>20</v>
+      <c r="L24" s="6" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M24" s="6" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N24" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+        <v>21</v>
+      </c>
+      <c r="O24" t="s">
+        <v>22</v>
+      </c>
+      <c r="P24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" s="2">
         <v>46162</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D25" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E25" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G25">
         <v>5</v>
@@ -1858,34 +2078,42 @@
         <f t="array" ref="K25">_xlfn.IFS(I25&lt;750, "Low", AND(I25&gt;=750, I25&lt;=1499), "Medium", AND(I25&gt;=1500, I25&lt;=2499), "High", I25&gt;=2500, "Excellent")</f>
         <v>High</v>
       </c>
-      <c r="L25" t="s">
-        <v>27</v>
-      </c>
-      <c r="M25" t="s">
-        <v>20</v>
+      <c r="L25" s="6" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M25" s="6" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N25" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+        <v>29</v>
+      </c>
+      <c r="O25" t="s">
+        <v>22</v>
+      </c>
+      <c r="P25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
       <c r="A26" s="2">
         <v>46168</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D26" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E26" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F26" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G26">
         <v>7</v>
@@ -1904,34 +2132,42 @@
         <f t="array" ref="K26">_xlfn.IFS(I26&lt;750, "Low", AND(I26&gt;=750, I26&lt;=1499), "Medium", AND(I26&gt;=1500, I26&lt;=2499), "High", I26&gt;=2500, "Excellent")</f>
         <v>Low</v>
       </c>
-      <c r="L26" t="s">
-        <v>19</v>
-      </c>
-      <c r="M26" t="s">
-        <v>20</v>
+      <c r="L26" s="6" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M26" s="6" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="N26" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
+        <v>21</v>
+      </c>
+      <c r="O26" t="s">
+        <v>22</v>
+      </c>
+      <c r="P26" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
       <c r="A27" s="2">
         <v>46174</v>
       </c>
       <c r="B27" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F27" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G27">
         <v>3</v>
@@ -1950,34 +2186,42 @@
         <f t="array" ref="K27">_xlfn.IFS(I27&lt;750, "Low", AND(I27&gt;=750, I27&lt;=1499), "Medium", AND(I27&gt;=1500, I27&lt;=2499), "High", I27&gt;=2500, "Excellent")</f>
         <v>High</v>
       </c>
-      <c r="L27" t="s">
-        <v>27</v>
-      </c>
-      <c r="M27" t="s">
-        <v>37</v>
+      <c r="L27" s="6" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M27" s="6" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N27" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
+        <v>29</v>
+      </c>
+      <c r="O27" t="s">
+        <v>39</v>
+      </c>
+      <c r="P27" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
       <c r="A28" s="2">
         <v>46180</v>
       </c>
       <c r="B28" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C28" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D28" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F28" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G28">
         <v>4</v>
@@ -1996,34 +2240,42 @@
         <f t="array" ref="K28">_xlfn.IFS(I28&lt;750, "Low", AND(I28&gt;=750, I28&lt;=1499), "Medium", AND(I28&gt;=1500, I28&lt;=2499), "High", I28&gt;=2500, "Excellent")</f>
         <v>Excellent</v>
       </c>
-      <c r="L28" t="s">
-        <v>19</v>
-      </c>
-      <c r="M28" t="s">
-        <v>20</v>
+      <c r="L28" s="6" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M28" s="6" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N28" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="29" spans="1:14">
+      <c r="O28" t="s">
+        <v>22</v>
+      </c>
+      <c r="P28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
       <c r="A29" s="2">
         <v>46186</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C29" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D29" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E29" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F29" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G29">
         <v>25</v>
@@ -2042,34 +2294,42 @@
         <f t="array" ref="K29">_xlfn.IFS(I29&lt;750, "Low", AND(I29&gt;=750, I29&lt;=1499), "Medium", AND(I29&gt;=1500, I29&lt;=2499), "High", I29&gt;=2500, "Excellent")</f>
         <v>Medium</v>
       </c>
-      <c r="L29" t="s">
-        <v>19</v>
-      </c>
-      <c r="M29" t="s">
-        <v>20</v>
+      <c r="L29" s="6" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M29" s="6" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="N29" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
+        <v>21</v>
+      </c>
+      <c r="O29" t="s">
+        <v>22</v>
+      </c>
+      <c r="P29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
       <c r="A30" s="2">
         <v>46192</v>
       </c>
       <c r="B30" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D30" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E30" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F30" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G30">
         <v>5</v>
@@ -2088,34 +2348,42 @@
         <f t="array" ref="K30">_xlfn.IFS(I30&lt;750, "Low", AND(I30&gt;=750, I30&lt;=1499), "Medium", AND(I30&gt;=1500, I30&lt;=2499), "High", I30&gt;=2500, "Excellent")</f>
         <v>Medium</v>
       </c>
-      <c r="L30" t="s">
-        <v>27</v>
-      </c>
-      <c r="M30" t="s">
-        <v>20</v>
+      <c r="L30" s="6" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M30" s="6" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N30" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
+        <v>29</v>
+      </c>
+      <c r="O30" t="s">
+        <v>22</v>
+      </c>
+      <c r="P30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
       <c r="A31" s="2">
         <v>46198</v>
       </c>
       <c r="B31" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C31" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D31" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E31" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F31" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -2134,25 +2402,33 @@
         <f t="array" ref="K31">_xlfn.IFS(I31&lt;750, "Low", AND(I31&gt;=750, I31&lt;=1499), "Medium", AND(I31&gt;=1500, I31&lt;=2499), "High", I31&gt;=2500, "Excellent")</f>
         <v>Low</v>
       </c>
-      <c r="L31" t="s">
-        <v>19</v>
-      </c>
-      <c r="M31" t="s">
-        <v>50</v>
+      <c r="L31" s="6" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M31" s="6" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N31" t="s">
-        <v>28</v>
+        <v>21</v>
+      </c>
+      <c r="O31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P31" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N31" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:P31" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31106EF7-38D2-4700-A08C-549C6A93CE37}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="17.25"/>
   <cols>
     <col min="1" max="1" width="56" style="3" bestFit="1" customWidth="1"/>
@@ -2163,7 +2439,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C1" s="3">
         <f>SUM(Sales!H:H)</f>
@@ -2172,7 +2448,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C2" s="3">
         <f>C1/COUNTA(Sales!A2:A31)</f>
@@ -2181,7 +2457,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C3" s="3">
         <f>MIN(Sales!I:I)</f>
@@ -2190,7 +2466,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C4" s="3">
         <f>MAX(Sales!I:I)</f>
@@ -2199,7 +2475,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C5" s="3">
         <f>COUNT(Sales!I:I)</f>
@@ -2208,7 +2484,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C6" s="3">
         <f>COUNTA(Sales!A2:A31)</f>
@@ -2217,18 +2493,88 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="3">
+        <f>COUNTIF(Sales!O:O, "=Completed")</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" s="3">
+        <f>COUNTIFS(Sales!O:O, "=Completed", Sales!B:B, "=East")</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" s="3">
+        <f>SUMIF(Sales!B:B, "=East", Sales!I:I)</f>
+        <v>12480</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" s="3">
+        <f>SUMIFS(Sales!I:I, Sales!B:B, "East", Sales!O:O, "Completed")</f>
+        <v>12480</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" s="3">
+        <f>AVERAGEIF(Sales!E:E, "Electronics", Sales!I:I)</f>
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="3">
+        <f>AVERAGEIFS(Sales!I:I, Sales!B:B, "East", Sales!O:O, "Completed")</f>
+        <v>1560</v>
       </c>
     </row>
   </sheetData>
